--- a/data/trans_dic/P33B_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R3-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,12; 30,73</t>
+          <t>22,57; 29,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,96; 40,4</t>
+          <t>34,99; 40,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,22; 35,7</t>
+          <t>31,08; 35,07</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 14,39</t>
+          <t>12,28; 15,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,79; 17,96</t>
+          <t>16,96; 19,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,22; 15,69</t>
+          <t>14,79; 17,13</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 15,58</t>
+          <t>10,56; 16,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,32; 16,99</t>
+          <t>12,67; 17,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,7; 15,47</t>
+          <t>12,25; 15,84</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,15; 16,18</t>
+          <t>14,19; 16,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,12; 21,97</t>
+          <t>20,8; 23,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,06; 18,77</t>
+          <t>17,97; 19,62</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>139748</t>
+          <t>149313</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>284430</t>
+          <t>312206</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424178</t>
+          <t>461519</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>124183; 158247</t>
+          <t>130568; 168839</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>263278; 304280</t>
+          <t>287414; 332905</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>395855; 452662</t>
+          <t>435019; 490990</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>278471</t>
+          <t>302543</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>353280</t>
+          <t>398440</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>631751</t>
+          <t>700983</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>194553; 329449</t>
+          <t>273776; 339790</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>263921; 402004</t>
+          <t>368357; 430790</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>508112; 710240</t>
+          <t>650900; 753665</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81951</t>
+          <t>92719</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94845</t>
+          <t>109019</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>176795</t>
+          <t>201738</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64026; 100623</t>
+          <t>75026; 117739</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81352; 112188</t>
+          <t>93116; 127173</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>152805; 202117</t>
+          <t>177070; 228922</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>500169</t>
+          <t>544575</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>732555</t>
+          <t>819665</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1232724</t>
+          <t>1364240</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>384806; 558352</t>
+          <t>499372; 593304</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>588625; 802156</t>
+          <t>775430; 863889</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1069728; 1333143</t>
+          <t>1302047; 1421800</t>
         </is>
       </c>
     </row>
